--- a/01_Hardware/BOM/Sample-BOM_JLCSMT.xlsx
+++ b/01_Hardware/BOM/Sample-BOM_JLCSMT.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="211">
   <si>
     <t xml:space="preserve">Comment</t>
   </si>
@@ -628,7 +628,10 @@
     <t xml:space="preserve">SW800,SW801</t>
   </si>
   <si>
-    <t xml:space="preserve">Button_Switch_SMD:SW_SPST_PTS645</t>
+    <t xml:space="preserve">SMD,6x3.6mm </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C318938 </t>
   </si>
   <si>
     <t xml:space="preserve">TPS61287</t>
@@ -1889,77 +1892,77 @@
         <v>189</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>82</v>
+        <v>190</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="1048461" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
